--- a/data/gravel/Fairlight Holt 2.0 2025.xlsx
+++ b/data/gravel/Fairlight Holt 2.0 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EF317F-3B87-7C48-8A91-B46D69ECF21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF07F99-F73D-0F4F-BDD4-6DE97A728417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="3800" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2900" yWindow="3300" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -257,12 +257,6 @@
     <t>Size</t>
   </si>
   <si>
-    <t>rider_min_spec</t>
-  </si>
-  <si>
-    <t>rider_max_spec</t>
-  </si>
-  <si>
     <t>Fairlight</t>
   </si>
   <si>
@@ -377,17 +371,17 @@
     <t>20% sag</t>
   </si>
   <si>
-    <t>a8:f37</t>
-  </si>
-  <si>
-    <t>Holt 2.0 (100 mm travel)</t>
+    <t>a8:f35</t>
+  </si>
+  <si>
+    <t>Holt 2.0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -440,6 +434,11 @@
       <name val="Futura"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF191919"/>
+      <name val="Futura Medium"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -461,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -473,6 +472,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z77"/>
+  <dimension ref="A1:Z75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
@@ -791,7 +791,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -815,7 +815,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
@@ -823,30 +823,30 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="C8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>102</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -855,81 +855,81 @@
         <v>73</v>
       </c>
       <c r="K8" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="S8" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="T8" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="U8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="T8" s="9" t="s">
+      <c r="V8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="W8" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="V8" s="9" t="s">
+      <c r="X8" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="W8" s="9" t="s">
+      <c r="Y8" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="X8" s="9" t="s">
+      <c r="Z8" s="9" t="s">
         <v>95</v>
-      </c>
-      <c r="Y8" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z8" s="9" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="10">
-        <v>100</v>
-      </c>
-      <c r="D9" s="10">
-        <v>100</v>
-      </c>
-      <c r="E9" s="10">
-        <v>100</v>
-      </c>
-      <c r="F9" s="10">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="2">
+        <v>120</v>
+      </c>
+      <c r="D9" s="2">
+        <v>120</v>
+      </c>
+      <c r="E9" s="2">
+        <v>120</v>
+      </c>
+      <c r="F9" s="2">
+        <v>120</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L9" s="10">
         <v>385</v>
@@ -981,29 +981,29 @@
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="10">
+      <c r="B10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="2">
         <v>385</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="2">
         <v>425</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="11">
         <v>465</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="11">
         <v>510</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L10" s="10">
         <v>425</v>
@@ -1055,29 +1055,29 @@
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="10">
-        <v>588.1</v>
-      </c>
-      <c r="D11" s="10">
-        <v>613</v>
-      </c>
-      <c r="E11" s="10">
-        <v>635.6</v>
-      </c>
-      <c r="F11" s="10">
-        <v>665.7</v>
+      <c r="B11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="2">
+        <v>590.9</v>
+      </c>
+      <c r="D11" s="2">
+        <v>615.79999999999995</v>
+      </c>
+      <c r="E11" s="11">
+        <v>638.4</v>
+      </c>
+      <c r="F11" s="11">
+        <v>668.6</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L11" s="10">
         <v>465</v>
@@ -1129,29 +1129,29 @@
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="10">
-        <v>75.3</v>
-      </c>
-      <c r="D12" s="10">
-        <v>75.3</v>
-      </c>
-      <c r="E12" s="10">
-        <v>75.2</v>
-      </c>
-      <c r="F12" s="10">
-        <v>75.2</v>
+      <c r="B12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="2">
+        <v>74.3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>74.3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>74.3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>74.3</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L12" s="10">
         <v>510</v>
@@ -1201,22 +1201,22 @@
     </row>
     <row r="13" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="10">
-        <v>76.2</v>
-      </c>
-      <c r="D13" s="10">
-        <v>76.2</v>
-      </c>
-      <c r="E13" s="10">
-        <v>76.2</v>
-      </c>
-      <c r="F13" s="10">
-        <v>76.099999999999994</v>
+        <v>104</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="2">
+        <v>75.3</v>
+      </c>
+      <c r="D13" s="2">
+        <v>75.3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>75.3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>75.2</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
@@ -1241,31 +1241,31 @@
     </row>
     <row r="14" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="10">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="D14" s="10">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="E14" s="10">
-        <v>76.099999999999994</v>
-      </c>
-      <c r="F14" s="10">
-        <v>76</v>
+        <v>105</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="2">
+        <v>75.2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>75.2</v>
+      </c>
+      <c r="E14" s="2">
+        <v>75.2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>75.099999999999994</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>98</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>100</v>
       </c>
       <c r="L14" s="10">
         <v>385</v>
@@ -1315,31 +1315,31 @@
     </row>
     <row r="15" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="10">
-        <v>76</v>
-      </c>
-      <c r="D15" s="10">
-        <v>76</v>
-      </c>
-      <c r="E15" s="10">
-        <v>76</v>
-      </c>
-      <c r="F15" s="10">
-        <v>75.900000000000006</v>
+        <v>106</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="2">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="D15" s="2">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="E15" s="2">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="F15" s="2">
+        <v>75</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L15" s="10">
         <v>425</v>
@@ -1391,29 +1391,29 @@
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="10">
-        <v>68</v>
-      </c>
-      <c r="D16" s="10">
-        <v>68</v>
-      </c>
-      <c r="E16" s="10">
-        <v>67.900000000000006</v>
-      </c>
-      <c r="F16" s="10">
-        <v>67.900000000000006</v>
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="2">
+        <v>67</v>
+      </c>
+      <c r="D16" s="2">
+        <v>67</v>
+      </c>
+      <c r="E16" s="2">
+        <v>67</v>
+      </c>
+      <c r="F16" s="2">
+        <v>67</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
       <c r="J16" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L16" s="10">
         <v>465</v>
@@ -1465,29 +1465,29 @@
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="10">
+      <c r="B17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="2">
         <v>435</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="2">
         <v>435</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="2">
         <v>435</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="2">
         <v>435</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L17" s="10">
         <v>510</v>
@@ -1539,19 +1539,19 @@
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="10">
+      <c r="B18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="2">
         <v>44</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="2">
         <v>44</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="2">
         <v>44</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="2">
         <v>44</v>
       </c>
       <c r="G18" s="8"/>
@@ -1579,29 +1579,29 @@
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="10">
-        <v>1130</v>
-      </c>
-      <c r="D19" s="10">
-        <v>1155</v>
-      </c>
-      <c r="E19" s="10">
-        <v>1179</v>
-      </c>
-      <c r="F19" s="10">
-        <v>1212</v>
+      <c r="B19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1138</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1163</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1187</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1220</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L19" s="10">
         <v>385</v>
@@ -1653,29 +1653,29 @@
       <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="10">
-        <v>70</v>
-      </c>
-      <c r="D20" s="10">
-        <v>70</v>
-      </c>
-      <c r="E20" s="10">
-        <v>70</v>
-      </c>
-      <c r="F20" s="10">
-        <v>70</v>
+      <c r="B20" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="2">
+        <v>63</v>
+      </c>
+      <c r="D20" s="2">
+        <v>63</v>
+      </c>
+      <c r="E20" s="2">
+        <v>63</v>
+      </c>
+      <c r="F20" s="2">
+        <v>63</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L20" s="10">
         <v>425</v>
@@ -1727,29 +1727,29 @@
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="10">
+      <c r="B21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="2">
         <v>100</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="2">
         <v>100</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="2">
         <v>110</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="2">
         <v>130</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L21" s="8">
         <v>465</v>
@@ -1801,29 +1801,29 @@
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C22" s="10">
-        <v>608</v>
-      </c>
-      <c r="D22" s="10">
-        <v>608</v>
-      </c>
-      <c r="E22" s="10">
-        <v>617</v>
-      </c>
-      <c r="F22" s="10">
-        <v>635</v>
+      <c r="B22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="2">
+        <v>616</v>
+      </c>
+      <c r="D22" s="2">
+        <v>616</v>
+      </c>
+      <c r="E22" s="2">
+        <v>625</v>
+      </c>
+      <c r="F22" s="2">
+        <v>643</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L22" s="8">
         <v>510</v>
@@ -1875,20 +1875,20 @@
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="10">
-        <v>436</v>
-      </c>
-      <c r="D23" s="10">
-        <v>460</v>
-      </c>
-      <c r="E23" s="10">
-        <v>480</v>
-      </c>
-      <c r="F23" s="10">
-        <v>505</v>
+      <c r="B23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="2">
+        <v>425</v>
+      </c>
+      <c r="D23" s="2">
+        <v>450</v>
+      </c>
+      <c r="E23" s="2">
+        <v>470</v>
+      </c>
+      <c r="F23" s="2">
+        <v>495</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -1910,20 +1910,20 @@
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="10">
-        <v>486</v>
-      </c>
-      <c r="D24" s="10">
-        <v>486</v>
-      </c>
-      <c r="E24" s="10">
-        <v>486</v>
-      </c>
-      <c r="F24" s="10">
-        <v>486</v>
+      <c r="B24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="2">
+        <v>507</v>
+      </c>
+      <c r="D24" s="2">
+        <v>507</v>
+      </c>
+      <c r="E24" s="2">
+        <v>507</v>
+      </c>
+      <c r="F24" s="2">
+        <v>507</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="25" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="8"/>
@@ -2132,20 +2132,16 @@
         <v>28</v>
       </c>
       <c r="C34" s="2">
-        <f>C36</f>
         <v>160</v>
       </c>
       <c r="D34" s="2">
-        <f>AVERAGE(D36,C37)</f>
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E34" s="2">
-        <f t="shared" ref="E34:G34" si="2">AVERAGE(E36,D37)</f>
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F34" s="2">
-        <f t="shared" si="2"/>
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
@@ -2156,316 +2152,278 @@
         <v>30</v>
       </c>
       <c r="C35" s="2">
-        <f>D34</f>
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D35" s="2">
-        <f t="shared" ref="D35:F35" si="3">E34</f>
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E35" s="2">
-        <f t="shared" si="3"/>
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F35" s="2">
-        <f>F37</f>
         <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="2">
-        <v>160</v>
-      </c>
-      <c r="D36" s="2">
-        <v>170</v>
-      </c>
-      <c r="E36" s="2">
-        <v>178</v>
-      </c>
-      <c r="F36" s="2">
-        <v>186</v>
-      </c>
+      <c r="L36" s="1"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" s="2">
-        <v>172</v>
-      </c>
-      <c r="D37" s="2">
-        <v>180</v>
-      </c>
-      <c r="E37" s="2">
-        <v>188</v>
-      </c>
-      <c r="F37" s="2">
-        <v>195</v>
+        <v>31</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L38" s="1"/>
+      <c r="A38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>71</v>
+        <v>36</v>
+      </c>
+      <c r="B44" s="2">
+        <f>2.6*25.4</f>
+        <v>66.039999999999992</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B46" s="2">
-        <f>2.6*25.4</f>
-        <v>66.039999999999992</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="B47" s="2">
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="2">
-        <v>120</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>72</v>
+        <v>46</v>
+      </c>
+      <c r="B54" s="2">
+        <v>30.9</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B56" s="2">
-        <v>30.9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B58" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="B59" s="2">
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="2">
-        <v>180</v>
+        <v>53</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="B65" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="B66" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="2">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" s="2">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="B72" s="2">
+        <v>920</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B73" s="2">
+        <v>2995</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B74" s="2">
-        <v>920</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B75" s="2">
-        <v>2995</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>79</v>
+      <c r="B75" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Fairlight Holt 2.0 2025.xlsx
+++ b/data/gravel/Fairlight Holt 2.0 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF07F99-F73D-0F4F-BDD4-6DE97A728417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFA1921-540B-F14D-ACD8-DDF808782569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2900" yWindow="3300" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32840" yWindow="-19060" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -251,9 +251,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>threaded</t>
-  </si>
-  <si>
     <t>Size</t>
   </si>
   <si>
@@ -375,6 +372,9 @@
   </si>
   <si>
     <t>Holt 2.0</t>
+  </si>
+  <si>
+    <t>threaded 73</t>
   </si>
 </sst>
 </file>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
@@ -791,7 +791,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -815,7 +815,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
@@ -823,10 +823,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="22" x14ac:dyDescent="0.3">
@@ -834,81 +834,81 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8"/>
       <c r="J8" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="S8" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="T8" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="T8" s="9" t="s">
+      <c r="U8" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="V8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="V8" s="9" t="s">
+      <c r="W8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="W8" s="9" t="s">
+      <c r="X8" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="X8" s="9" t="s">
+      <c r="Y8" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="Y8" s="9" t="s">
+      <c r="Z8" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="Z8" s="9" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="2">
         <v>120</v>
@@ -926,10 +926,10 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>96</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>97</v>
       </c>
       <c r="L9" s="10">
         <v>385</v>
@@ -982,7 +982,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="2">
         <v>385</v>
@@ -1000,10 +1000,10 @@
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L10" s="10">
         <v>425</v>
@@ -1056,7 +1056,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="2">
         <v>590.9</v>
@@ -1074,10 +1074,10 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L11" s="10">
         <v>465</v>
@@ -1130,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="2">
         <v>74.3</v>
@@ -1148,10 +1148,10 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L12" s="10">
         <v>510</v>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="13" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="2">
         <v>75.3</v>
@@ -1241,10 +1241,10 @@
     </row>
     <row r="14" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" s="2">
         <v>75.2</v>
@@ -1262,10 +1262,10 @@
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L14" s="10">
         <v>385</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="15" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="2">
         <v>75.099999999999994</v>
@@ -1336,10 +1336,10 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L15" s="10">
         <v>425</v>
@@ -1392,7 +1392,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16" s="2">
         <v>67</v>
@@ -1410,10 +1410,10 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
       <c r="J16" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L16" s="10">
         <v>465</v>
@@ -1466,7 +1466,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="2">
         <v>435</v>
@@ -1484,10 +1484,10 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L17" s="10">
         <v>510</v>
@@ -1540,7 +1540,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" s="2">
         <v>44</v>
@@ -1580,7 +1580,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C19" s="2">
         <v>1138</v>
@@ -1598,10 +1598,10 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L19" s="10">
         <v>385</v>
@@ -1654,7 +1654,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2">
         <v>63</v>
@@ -1672,10 +1672,10 @@
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L20" s="10">
         <v>425</v>
@@ -1728,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" s="2">
         <v>100</v>
@@ -1746,10 +1746,10 @@
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L21" s="8">
         <v>465</v>
@@ -1802,7 +1802,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" s="2">
         <v>616</v>
@@ -1820,10 +1820,10 @@
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L22" s="8">
         <v>510</v>
@@ -1876,7 +1876,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="2">
         <v>425</v>
@@ -1911,7 +1911,7 @@
         <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" s="2">
         <v>507</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="25" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="8"/>
@@ -2180,7 +2180,7 @@
         <v>68</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2188,7 +2188,7 @@
         <v>69</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2196,7 +2196,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2204,7 +2204,7 @@
         <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
@@ -2225,8 +2225,7 @@
         <v>36</v>
       </c>
       <c r="B44" s="2">
-        <f>2.6*25.4</f>
-        <v>66.039999999999992</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -2264,18 +2263,24 @@
       <c r="A50" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="B50" s="2">
+        <v>148</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="B51" s="2">
+        <v>110</v>
+      </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -2296,7 +2301,7 @@
         <v>47</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -2335,7 +2340,7 @@
         <v>53</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -2423,7 +2428,7 @@
         <v>67</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Fairlight Holt 2.0 2025.xlsx
+++ b/data/gravel/Fairlight Holt 2.0 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFA1921-540B-F14D-ACD8-DDF808782569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3341FE31-BCD4-7341-BFBB-9230291597C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32840" yWindow="-19060" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>threaded 73</t>
+  </si>
+  <si>
+    <t>internal</t>
   </si>
 </sst>
 </file>
@@ -2347,6 +2350,9 @@
       <c r="A62" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="B62" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">

--- a/data/gravel/Fairlight Holt 2.0 2025.xlsx
+++ b/data/gravel/Fairlight Holt 2.0 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3341FE31-BCD4-7341-BFBB-9230291597C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF72158A-5640-EA4C-9CE7-5C55D09B860A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>internal</t>
+  </si>
+  <si>
+    <t>https://media.fairlightcycles.com/wp-content/uploads/2025/08/2560-x-1152-Banner-Master-Holt-2.0-Violet.jpg</t>
   </si>
 </sst>
 </file>
@@ -821,6 +824,11 @@
         <v>78</v>
       </c>
     </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>

--- a/data/gravel/Fairlight Holt 2.0 2025.xlsx
+++ b/data/gravel/Fairlight Holt 2.0 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF72158A-5640-EA4C-9CE7-5C55D09B860A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258BBBD0-2165-1240-8117-8D8A4F83F3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7100" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -263,9 +263,6 @@
     <t>steel</t>
   </si>
   <si>
-    <t>pounds</t>
-  </si>
-  <si>
     <t>external</t>
   </si>
   <si>
@@ -381,6 +378,15 @@
   </si>
   <si>
     <t>https://media.fairlightcycles.com/wp-content/uploads/2025/08/2560-x-1152-Banner-Master-Holt-2.0-Violet.jpg</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>London, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -775,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z75"/>
+  <dimension ref="A1:Z76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -797,7 +803,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -821,12 +827,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
@@ -834,10 +840,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="22" x14ac:dyDescent="0.3">
@@ -848,16 +854,16 @@
         <v>72</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>100</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>101</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
@@ -866,60 +872,60 @@
         <v>72</v>
       </c>
       <c r="K8" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="M8" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="N8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="O8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="P8" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="Q8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="R8" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="S8" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="T8" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="T8" s="9" t="s">
+      <c r="U8" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="V8" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="V8" s="9" t="s">
+      <c r="W8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="W8" s="9" t="s">
+      <c r="X8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="X8" s="9" t="s">
+      <c r="Y8" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="Y8" s="9" t="s">
+      <c r="Z8" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="Z8" s="9" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" s="2">
         <v>120</v>
@@ -937,10 +943,10 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="L9" s="10">
         <v>385</v>
@@ -993,7 +999,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" s="2">
         <v>385</v>
@@ -1011,10 +1017,10 @@
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L10" s="10">
         <v>425</v>
@@ -1067,7 +1073,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2">
         <v>590.9</v>
@@ -1085,10 +1091,10 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L11" s="10">
         <v>465</v>
@@ -1141,7 +1147,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="2">
         <v>74.3</v>
@@ -1159,10 +1165,10 @@
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L12" s="10">
         <v>510</v>
@@ -1212,10 +1218,10 @@
     </row>
     <row r="13" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C13" s="2">
         <v>75.3</v>
@@ -1252,10 +1258,10 @@
     </row>
     <row r="14" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" s="2">
         <v>75.2</v>
@@ -1273,10 +1279,10 @@
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
       <c r="J14" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L14" s="10">
         <v>385</v>
@@ -1326,10 +1332,10 @@
     </row>
     <row r="15" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="2">
         <v>75.099999999999994</v>
@@ -1347,10 +1353,10 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L15" s="10">
         <v>425</v>
@@ -1403,7 +1409,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="2">
         <v>67</v>
@@ -1421,10 +1427,10 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
       <c r="J16" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L16" s="10">
         <v>465</v>
@@ -1477,7 +1483,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C17" s="2">
         <v>435</v>
@@ -1495,10 +1501,10 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L17" s="10">
         <v>510</v>
@@ -1551,7 +1557,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="2">
         <v>44</v>
@@ -1591,7 +1597,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" s="2">
         <v>1138</v>
@@ -1609,10 +1615,10 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L19" s="10">
         <v>385</v>
@@ -1665,7 +1671,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="2">
         <v>63</v>
@@ -1683,10 +1689,10 @@
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
       <c r="J20" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L20" s="10">
         <v>425</v>
@@ -1739,7 +1745,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2">
         <v>100</v>
@@ -1757,10 +1763,10 @@
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
       <c r="J21" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L21" s="8">
         <v>465</v>
@@ -1813,7 +1819,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" s="2">
         <v>616</v>
@@ -1831,10 +1837,10 @@
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L22" s="8">
         <v>510</v>
@@ -1887,7 +1893,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" s="2">
         <v>425</v>
@@ -1922,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="2">
         <v>507</v>
@@ -2191,7 +2197,7 @@
         <v>68</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -2199,7 +2205,7 @@
         <v>69</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
@@ -2207,7 +2213,7 @@
         <v>70</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -2291,7 +2297,7 @@
         <v>44</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -2312,7 +2318,7 @@
         <v>47</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -2351,7 +2357,7 @@
         <v>53</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -2359,7 +2365,7 @@
         <v>54</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -2442,7 +2448,15 @@
         <v>67</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>76</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Fairlight Holt 2.0 2025.xlsx
+++ b/data/gravel/Fairlight Holt 2.0 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258BBBD0-2165-1240-8117-8D8A4F83F3F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7BB24C-3D3B-4645-AA5B-C55D55548430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7100" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="124">
   <si>
     <t>brand</t>
   </si>
@@ -387,6 +387,24 @@
   </si>
   <si>
     <t>London, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -781,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z76"/>
+  <dimension ref="A1:Z82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -2294,168 +2312,198 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="2">
-        <v>30.9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B56" s="2">
-        <v>38</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="2">
-        <v>180</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B60" s="2">
+        <v>30.9</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>113</v>
+        <v>48</v>
+      </c>
+      <c r="B62" s="2">
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B65" s="2">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="2">
-        <v>1</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>71</v>
+        <v>57</v>
+      </c>
+      <c r="B71" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B72" s="2">
-        <v>920</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="2">
-        <v>2995</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" s="2">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="2">
+        <v>2995</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>117</v>
       </c>
     </row>

--- a/data/gravel/Fairlight Holt 2.0 2025.xlsx
+++ b/data/gravel/Fairlight Holt 2.0 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7BB24C-3D3B-4645-AA5B-C55D55548430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DCE622-61EB-AB42-8196-CF45624176A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -365,9 +365,6 @@
     <t>20% sag</t>
   </si>
   <si>
-    <t>a8:f35</t>
-  </si>
-  <si>
     <t>Holt 2.0</t>
   </si>
   <si>
@@ -405,6 +402,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>seat_tube_angle_actual</t>
+  </si>
+  <si>
+    <t>a8:f36</t>
+  </si>
+  <si>
+    <t>Effective STA at stack (I computed this)</t>
   </si>
 </sst>
 </file>
@@ -799,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z82"/>
+  <dimension ref="A1:Z83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -821,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
@@ -850,7 +856,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
@@ -858,7 +864,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>109</v>
@@ -1162,7 +1168,7 @@
     </row>
     <row r="12" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>81</v>
@@ -1179,8 +1185,14 @@
       <c r="F12" s="2">
         <v>74.3</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="G12" s="8">
+        <f>C$23+C$22/TAN(C12*PI()/180)</f>
+        <v>598.14979103112341</v>
+      </c>
+      <c r="H12" s="8">
+        <f>D$23+D$22/TAN(D12*PI()/180)</f>
+        <v>623.14979103112341</v>
+      </c>
       <c r="I12" s="8"/>
       <c r="J12" s="10" t="s">
         <v>100</v>
@@ -1253,8 +1265,14 @@
       <c r="F13" s="2">
         <v>75.2</v>
       </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="G13" s="8">
+        <f>C$23+C$22/TAN(C13*PI()/180)</f>
+        <v>586.6045747577607</v>
+      </c>
+      <c r="H13" s="8">
+        <f>D$23+D$22/TAN(D13*PI()/180)</f>
+        <v>611.6045747577607</v>
+      </c>
       <c r="I13" s="8"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
@@ -1293,8 +1311,14 @@
       <c r="F14" s="2">
         <v>75.099999999999994</v>
       </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="G14" s="8">
+        <f>C$23+C$22/TAN(C14*PI()/180)</f>
+        <v>587.75422041204138</v>
+      </c>
+      <c r="H14" s="8">
+        <f>D$23+D$22/TAN(D14*PI()/180)</f>
+        <v>612.75422041204138</v>
+      </c>
       <c r="I14" s="8"/>
       <c r="J14" s="10" t="s">
         <v>94</v>
@@ -1367,8 +1391,14 @@
       <c r="F15" s="2">
         <v>75</v>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="G15" s="8">
+        <f>C$23+C$22/TAN(C15*PI()/180)</f>
+        <v>588.90492684228116</v>
+      </c>
+      <c r="H15" s="8">
+        <f>D$23+D$22/TAN(D15*PI()/180)</f>
+        <v>613.90492684228116</v>
+      </c>
       <c r="I15" s="8"/>
       <c r="J15" s="10" t="s">
         <v>98</v>
@@ -1978,13 +2008,23 @@
     </row>
     <row r="25" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="2">
+        <v>74.926842070000006</v>
+      </c>
+      <c r="D25" s="2">
+        <v>74.935514670000003</v>
+      </c>
+      <c r="E25" s="2">
+        <v>74.920334609999998</v>
+      </c>
+      <c r="F25" s="2">
+        <v>74.891255409999999</v>
+      </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
@@ -2003,7 +2043,7 @@
     </row>
     <row r="26" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="8"/>
@@ -2028,7 +2068,7 @@
     </row>
     <row r="27" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="8"/>
@@ -2053,7 +2093,7 @@
     </row>
     <row r="28" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
@@ -2076,209 +2116,226 @@
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="2">
-        <v>2220</v>
+        <v>22</v>
       </c>
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="2">
-        <v>700</v>
+        <v>23</v>
       </c>
       <c r="D31" s="2">
-        <v>700</v>
-      </c>
-      <c r="E31" s="2">
-        <v>700</v>
-      </c>
-      <c r="F31" s="2">
-        <v>700</v>
-      </c>
+        <v>2220</v>
+      </c>
+      <c r="F31" s="6"/>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="2">
+        <v>700</v>
+      </c>
+      <c r="D32" s="2">
+        <v>700</v>
+      </c>
+      <c r="E32" s="2">
+        <v>700</v>
+      </c>
+      <c r="F32" s="2">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C33" s="2">
         <f>2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="D32" s="2">
-        <f t="shared" ref="D32:F32" si="0">2.4*25.4</f>
+      <c r="D33" s="2">
+        <f t="shared" ref="D33:F33" si="0">2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E33" s="2">
         <f t="shared" si="0"/>
         <v>60.959999999999994</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F33" s="2">
         <f t="shared" si="0"/>
         <v>60.959999999999994</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C34" s="2">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="D33" s="2">
-        <f t="shared" ref="D33:F33" si="1">2.6*25.4</f>
+      <c r="D34" s="2">
+        <f t="shared" ref="D34:F34" si="1">2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E34" s="2">
         <f t="shared" si="1"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F34" s="2">
         <f t="shared" si="1"/>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="2">
-        <v>160</v>
-      </c>
-      <c r="D34" s="2">
-        <v>170</v>
-      </c>
-      <c r="E34" s="2">
-        <v>178</v>
-      </c>
-      <c r="F34" s="2">
-        <v>186</v>
-      </c>
-    </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="2">
+        <v>160</v>
+      </c>
+      <c r="D35" s="2">
+        <v>170</v>
+      </c>
+      <c r="E35" s="2">
+        <v>178</v>
+      </c>
+      <c r="F35" s="2">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C36" s="2">
         <v>172</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D36" s="2">
         <v>180</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E36" s="2">
         <v>188</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F36" s="2">
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L36" s="1"/>
-    </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="2">
-        <v>2.6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="B45" s="2">
+        <v>2.6</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="2">
-        <v>120</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="2">
         <v>120</v>
@@ -2286,225 +2343,233 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
+      </c>
+      <c r="B48" s="2">
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="2">
-        <v>148</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B51" s="2">
-        <v>110</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>118</v>
+        <v>43</v>
+      </c>
+      <c r="B52" s="2">
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B60" s="2">
-        <v>30.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>108</v>
+        <v>46</v>
+      </c>
+      <c r="B61" s="2">
+        <v>30.9</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B62" s="2">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+      <c r="B63" s="2">
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B65" s="2">
-        <v>180</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="B66" s="2">
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B71" s="2">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B72" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
+      </c>
+      <c r="B73" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B78" s="2">
-        <v>920</v>
+        <v>63</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B79" s="2">
-        <v>2995</v>
+        <v>920</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="B80" s="2">
+        <v>2995</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Fairlight Holt 2.0 2025.xlsx
+++ b/data/gravel/Fairlight Holt 2.0 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DCE622-61EB-AB42-8196-CF45624176A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7CAF99-2CB2-4946-B37E-A7405CCFC199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8620" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -407,10 +407,16 @@
     <t>seat_tube_angle_actual</t>
   </si>
   <si>
-    <t>a8:f36</t>
-  </si>
-  <si>
     <t>Effective STA at stack (I computed this)</t>
+  </si>
+  <si>
+    <t>a8:f38</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>100-120</t>
   </si>
 </sst>
 </file>
@@ -805,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z83"/>
+  <dimension ref="A1:Z85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -864,7 +870,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>109</v>
@@ -1186,11 +1192,11 @@
         <v>74.3</v>
       </c>
       <c r="G12" s="8">
-        <f>C$23+C$22/TAN(C12*PI()/180)</f>
+        <f t="shared" ref="G12:H15" si="0">C$23+C$22/TAN(C12*PI()/180)</f>
         <v>598.14979103112341</v>
       </c>
       <c r="H12" s="8">
-        <f>D$23+D$22/TAN(D12*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>623.14979103112341</v>
       </c>
       <c r="I12" s="8"/>
@@ -1266,11 +1272,11 @@
         <v>75.2</v>
       </c>
       <c r="G13" s="8">
-        <f>C$23+C$22/TAN(C13*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>586.6045747577607</v>
       </c>
       <c r="H13" s="8">
-        <f>D$23+D$22/TAN(D13*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>611.6045747577607</v>
       </c>
       <c r="I13" s="8"/>
@@ -1312,11 +1318,11 @@
         <v>75.099999999999994</v>
       </c>
       <c r="G14" s="8">
-        <f>C$23+C$22/TAN(C14*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>587.75422041204138</v>
       </c>
       <c r="H14" s="8">
-        <f>D$23+D$22/TAN(D14*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>612.75422041204138</v>
       </c>
       <c r="I14" s="8"/>
@@ -1392,11 +1398,11 @@
         <v>75</v>
       </c>
       <c r="G15" s="8">
-        <f>C$23+C$22/TAN(C15*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>588.90492684228116</v>
       </c>
       <c r="H15" s="8">
-        <f>D$23+D$22/TAN(D15*PI()/180)</f>
+        <f t="shared" si="0"/>
         <v>613.90492684228116</v>
       </c>
       <c r="I15" s="8"/>
@@ -2011,7 +2017,7 @@
         <v>8</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2">
         <v>74.926842070000006</v>
@@ -2043,13 +2049,21 @@
     </row>
     <row r="26" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+        <v>101</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="2">
+        <v>120</v>
+      </c>
+      <c r="D26" s="2">
+        <v>120</v>
+      </c>
+      <c r="E26" s="2">
+        <v>120</v>
+      </c>
+      <c r="F26" s="2">
+        <v>120</v>
+      </c>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
@@ -2068,13 +2082,21 @@
     </row>
     <row r="27" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
+        <v>126</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="2">
+        <v>20</v>
+      </c>
+      <c r="D27" s="2">
+        <v>20</v>
+      </c>
+      <c r="E27" s="2">
+        <v>20</v>
+      </c>
+      <c r="F27" s="2">
+        <v>20</v>
+      </c>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
@@ -2093,7 +2115,7 @@
     </row>
     <row r="28" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
@@ -2118,7 +2140,7 @@
     </row>
     <row r="29" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="8"/>
@@ -2141,434 +2163,484 @@
       <c r="T29" s="5"/>
       <c r="U29" s="5"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+    </row>
+    <row r="31" spans="1:26" ht="22" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="2">
-        <v>2220</v>
-      </c>
-      <c r="F31" s="6"/>
+        <v>21</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="2">
-        <v>700</v>
-      </c>
-      <c r="D32" s="2">
-        <v>700</v>
-      </c>
-      <c r="E32" s="2">
-        <v>700</v>
-      </c>
-      <c r="F32" s="2">
-        <v>700</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F32" s="6"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2220</v>
+      </c>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="2">
+        <v>700</v>
+      </c>
+      <c r="D34" s="2">
+        <v>700</v>
+      </c>
+      <c r="E34" s="2">
+        <v>700</v>
+      </c>
+      <c r="F34" s="2">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C35" s="2">
         <f>2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="D33" s="2">
-        <f t="shared" ref="D33:F33" si="0">2.4*25.4</f>
+      <c r="D35" s="2">
+        <f t="shared" ref="D35:F35" si="1">2.4*25.4</f>
         <v>60.959999999999994</v>
       </c>
-      <c r="E33" s="2">
-        <f t="shared" si="0"/>
+      <c r="E35" s="2">
+        <f t="shared" si="1"/>
         <v>60.959999999999994</v>
       </c>
-      <c r="F33" s="2">
-        <f t="shared" si="0"/>
+      <c r="F35" s="2">
+        <f t="shared" si="1"/>
         <v>60.959999999999994</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C36" s="2">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="D34" s="2">
-        <f t="shared" ref="D34:F34" si="1">2.6*25.4</f>
+      <c r="D36" s="2">
+        <f t="shared" ref="D36:F36" si="2">2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="E34" s="2">
-        <f t="shared" si="1"/>
+      <c r="E36" s="2">
+        <f t="shared" si="2"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="F34" s="2">
-        <f t="shared" si="1"/>
+      <c r="F36" s="2">
+        <f t="shared" si="2"/>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C37" s="2">
         <v>160</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D37" s="2">
         <v>170</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E37" s="2">
         <v>178</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F37" s="2">
         <v>186</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="2">
-        <v>172</v>
-      </c>
-      <c r="D36" s="2">
-        <v>180</v>
-      </c>
-      <c r="E36" s="2">
-        <v>188</v>
-      </c>
-      <c r="F36" s="2">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="C38" s="2">
+        <v>172</v>
+      </c>
+      <c r="D38" s="2">
+        <v>180</v>
+      </c>
+      <c r="E38" s="2">
+        <v>188</v>
+      </c>
+      <c r="F38" s="2">
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>106</v>
-      </c>
+      <c r="L39" s="1"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>107</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" s="2">
-        <v>2.6</v>
+        <v>34</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B47" s="2">
-        <v>120</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="2">
-        <v>120</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
+      </c>
+      <c r="B50" s="2">
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="2">
-        <v>148</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="2">
-        <v>110</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>117</v>
+        <v>42</v>
+      </c>
+      <c r="B53" s="2">
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>118</v>
+        <v>43</v>
+      </c>
+      <c r="B54" s="2">
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B61" s="2">
-        <v>30.9</v>
+        <v>44</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>108</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B63" s="2">
-        <v>38</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="B65" s="2">
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B66" s="2">
-        <v>180</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>76</v>
+        <v>51</v>
+      </c>
+      <c r="B68" s="2">
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B72" s="2">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B73" s="2">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="B74" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B75" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B79" s="2">
-        <v>920</v>
+        <v>62</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B80" s="2">
-        <v>2995</v>
+        <v>63</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="B81" s="2">
+        <v>920</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>114</v>
+        <v>65</v>
+      </c>
+      <c r="B82" s="2">
+        <v>2995</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>116</v>
       </c>
     </row>

--- a/data/gravel/Fairlight Holt 2.0 2025.xlsx
+++ b/data/gravel/Fairlight Holt 2.0 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7CAF99-2CB2-4946-B37E-A7405CCFC199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09FB56A-C907-0C46-991E-9EADF8580798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8620" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40500" yWindow="-22420" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -811,16 +811,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z85"/>
+  <dimension ref="A1:AP85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
     <col min="3" max="5" width="10.77734375" style="2"/>
     <col min="6" max="6" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.77734375" style="2"/>
+    <col min="7" max="24" width="10.77734375" style="2"/>
+    <col min="25" max="27" width="11.109375" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="10.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -828,7 +830,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -836,7 +838,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -844,7 +846,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -852,7 +854,7 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -860,12 +862,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -876,7 +878,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -897,60 +899,106 @@
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
-      <c r="I8"/>
+      <c r="I8" s="7"/>
       <c r="J8" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="R8" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="U8" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="V8" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="W8" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="X8" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y8"/>
+      <c r="Z8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA8" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="AB8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="AC8" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="N8" s="9" t="s">
+      <c r="AD8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="O8" s="9" t="s">
+      <c r="AE8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="AF8" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="AG8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="R8" s="9" t="s">
+      <c r="AH8" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="S8" s="9" t="s">
+      <c r="AI8" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="T8" s="9" t="s">
+      <c r="AJ8" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="AK8" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="V8" s="9" t="s">
+      <c r="AL8" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="W8" s="9" t="s">
+      <c r="AM8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="X8" s="9" t="s">
+      <c r="AN8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="Y8" s="9" t="s">
+      <c r="AO8" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="Z8" s="9" t="s">
+      <c r="AP8" s="9" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>101</v>
       </c>
@@ -972,59 +1020,105 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="10" t="s">
-        <v>94</v>
+      <c r="J9" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="K9" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="U9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="V9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="W9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="X9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB9" s="10">
         <v>385</v>
       </c>
-      <c r="M9" s="10">
+      <c r="AC9" s="10">
         <v>588.1</v>
       </c>
-      <c r="N9" s="10">
+      <c r="AD9" s="10">
         <v>75.3</v>
       </c>
-      <c r="O9" s="10">
+      <c r="AE9" s="10">
         <v>76.2</v>
       </c>
-      <c r="P9" s="10">
+      <c r="AF9" s="10">
         <v>76.099999999999994</v>
       </c>
-      <c r="Q9" s="10">
+      <c r="AG9" s="10">
         <v>76</v>
       </c>
-      <c r="R9" s="10">
+      <c r="AH9" s="10">
         <v>68</v>
       </c>
-      <c r="S9" s="10">
+      <c r="AI9" s="10">
         <v>435</v>
       </c>
-      <c r="T9" s="10">
+      <c r="AJ9" s="10">
         <v>44</v>
       </c>
-      <c r="U9" s="10">
+      <c r="AK9" s="10">
         <v>1130</v>
       </c>
-      <c r="V9" s="10">
+      <c r="AL9" s="10">
         <v>70</v>
       </c>
-      <c r="W9" s="10">
+      <c r="AM9" s="10">
         <v>100</v>
       </c>
-      <c r="X9" s="10">
+      <c r="AN9" s="10">
         <v>608</v>
       </c>
-      <c r="Y9" s="10">
+      <c r="AO9" s="10">
         <v>436</v>
       </c>
-      <c r="Z9" s="10">
+      <c r="AP9" s="10">
         <v>486</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1046,59 +1140,105 @@
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
-      <c r="J10" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>95</v>
+      <c r="J10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="10">
+        <v>385</v>
       </c>
       <c r="L10" s="10">
         <v>425</v>
       </c>
       <c r="M10" s="10">
+        <v>465</v>
+      </c>
+      <c r="N10" s="10">
+        <v>510</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="P10" s="10">
+        <v>385</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>425</v>
+      </c>
+      <c r="R10" s="10">
+        <v>465</v>
+      </c>
+      <c r="S10" s="10">
+        <v>510</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="U10" s="10">
+        <v>385</v>
+      </c>
+      <c r="V10" s="10">
+        <v>425</v>
+      </c>
+      <c r="W10" s="8">
+        <v>465</v>
+      </c>
+      <c r="X10" s="8">
+        <v>510</v>
+      </c>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA10" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB10" s="10">
+        <v>425</v>
+      </c>
+      <c r="AC10" s="10">
         <v>613</v>
       </c>
-      <c r="N10" s="10">
+      <c r="AD10" s="10">
         <v>75.3</v>
       </c>
-      <c r="O10" s="10">
+      <c r="AE10" s="10">
         <v>76.2</v>
       </c>
-      <c r="P10" s="10">
+      <c r="AF10" s="10">
         <v>76.099999999999994</v>
       </c>
-      <c r="Q10" s="10">
+      <c r="AG10" s="10">
         <v>76</v>
       </c>
-      <c r="R10" s="10">
+      <c r="AH10" s="10">
         <v>68</v>
       </c>
-      <c r="S10" s="10">
+      <c r="AI10" s="10">
         <v>435</v>
       </c>
-      <c r="T10" s="10">
+      <c r="AJ10" s="10">
         <v>44</v>
       </c>
-      <c r="U10" s="10">
+      <c r="AK10" s="10">
         <v>1155</v>
       </c>
-      <c r="V10" s="10">
+      <c r="AL10" s="10">
         <v>70</v>
       </c>
-      <c r="W10" s="10">
+      <c r="AM10" s="10">
         <v>100</v>
       </c>
-      <c r="X10" s="10">
+      <c r="AN10" s="10">
         <v>608</v>
       </c>
-      <c r="Y10" s="10">
+      <c r="AO10" s="10">
         <v>460</v>
       </c>
-      <c r="Z10" s="10">
+      <c r="AP10" s="10">
         <v>486</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -1120,59 +1260,105 @@
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
-      <c r="J11" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>95</v>
+      <c r="J11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="10">
+        <v>588.1</v>
       </c>
       <c r="L11" s="10">
-        <v>465</v>
+        <v>613</v>
       </c>
       <c r="M11" s="10">
         <v>635.6</v>
       </c>
       <c r="N11" s="10">
+        <v>665.7</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="P11" s="10">
+        <v>589.79999999999995</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>614.70000000000005</v>
+      </c>
+      <c r="R11" s="10">
+        <v>637.29999999999995</v>
+      </c>
+      <c r="S11" s="10">
+        <v>667.5</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="U11" s="10">
+        <v>590.9</v>
+      </c>
+      <c r="V11" s="10">
+        <v>615.79999999999995</v>
+      </c>
+      <c r="W11" s="8">
+        <v>638.4</v>
+      </c>
+      <c r="X11" s="8">
+        <v>668.6</v>
+      </c>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA11" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB11" s="10">
+        <v>465</v>
+      </c>
+      <c r="AC11" s="10">
+        <v>635.6</v>
+      </c>
+      <c r="AD11" s="10">
         <v>75.2</v>
       </c>
-      <c r="O11" s="10">
+      <c r="AE11" s="10">
         <v>76.2</v>
       </c>
-      <c r="P11" s="10">
+      <c r="AF11" s="10">
         <v>76.099999999999994</v>
       </c>
-      <c r="Q11" s="10">
+      <c r="AG11" s="10">
         <v>76</v>
       </c>
-      <c r="R11" s="10">
+      <c r="AH11" s="10">
         <v>67.900000000000006</v>
       </c>
-      <c r="S11" s="10">
+      <c r="AI11" s="10">
         <v>435</v>
       </c>
-      <c r="T11" s="10">
+      <c r="AJ11" s="10">
         <v>44</v>
       </c>
-      <c r="U11" s="10">
+      <c r="AK11" s="10">
         <v>1179</v>
       </c>
-      <c r="V11" s="10">
+      <c r="AL11" s="10">
         <v>70</v>
       </c>
-      <c r="W11" s="10">
+      <c r="AM11" s="10">
         <v>110</v>
       </c>
-      <c r="X11" s="10">
+      <c r="AN11" s="10">
         <v>617</v>
       </c>
-      <c r="Y11" s="10">
+      <c r="AO11" s="10">
         <v>480</v>
       </c>
-      <c r="Z11" s="10">
+      <c r="AP11" s="10">
         <v>486</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>123</v>
       </c>
@@ -1200,59 +1386,105 @@
         <v>623.14979103112341</v>
       </c>
       <c r="I12" s="8"/>
-      <c r="J12" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>95</v>
+      <c r="J12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="10">
+        <v>75.3</v>
       </c>
       <c r="L12" s="10">
-        <v>510</v>
+        <v>75.3</v>
       </c>
       <c r="M12" s="10">
-        <v>665.7</v>
+        <v>75.2</v>
       </c>
       <c r="N12" s="10">
         <v>75.2</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="P12" s="10">
+        <v>74.7</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>74.7</v>
+      </c>
+      <c r="R12" s="10">
+        <v>74.7</v>
+      </c>
+      <c r="S12" s="10">
+        <v>74.7</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="U12" s="10">
+        <v>74.3</v>
+      </c>
+      <c r="V12" s="10">
+        <v>74.3</v>
+      </c>
+      <c r="W12" s="5">
+        <v>74.3</v>
+      </c>
+      <c r="X12" s="5">
+        <v>74.3</v>
+      </c>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA12" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB12" s="10">
+        <v>510</v>
+      </c>
+      <c r="AC12" s="10">
+        <v>665.7</v>
+      </c>
+      <c r="AD12" s="10">
+        <v>75.2</v>
+      </c>
+      <c r="AE12" s="10">
         <v>76.099999999999994</v>
       </c>
-      <c r="P12" s="10">
+      <c r="AF12" s="10">
         <v>76</v>
       </c>
-      <c r="Q12" s="10">
+      <c r="AG12" s="10">
         <v>75.900000000000006</v>
       </c>
-      <c r="R12" s="10">
+      <c r="AH12" s="10">
         <v>67.900000000000006</v>
       </c>
-      <c r="S12" s="10">
+      <c r="AI12" s="10">
         <v>435</v>
       </c>
-      <c r="T12" s="10">
+      <c r="AJ12" s="10">
         <v>44</v>
       </c>
-      <c r="U12" s="10">
+      <c r="AK12" s="10">
         <v>1212</v>
       </c>
-      <c r="V12" s="10">
+      <c r="AL12" s="10">
         <v>70</v>
       </c>
-      <c r="W12" s="10">
+      <c r="AM12" s="10">
         <v>130</v>
       </c>
-      <c r="X12" s="10">
+      <c r="AN12" s="10">
         <v>635</v>
       </c>
-      <c r="Y12" s="10">
+      <c r="AO12" s="10">
         <v>505</v>
       </c>
-      <c r="Z12" s="10">
+      <c r="AP12" s="10">
         <v>486</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>102</v>
       </c>
@@ -1280,25 +1512,71 @@
         <v>611.6045747577607</v>
       </c>
       <c r="I13" s="8"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
+      <c r="J13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="10">
+        <v>76.2</v>
+      </c>
+      <c r="L13" s="10">
+        <v>76.2</v>
+      </c>
+      <c r="M13" s="10">
+        <v>76.2</v>
+      </c>
+      <c r="N13" s="10">
+        <v>76.099999999999994</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="P13" s="10">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="R13" s="10">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="S13" s="10">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="U13" s="10">
+        <v>75.3</v>
+      </c>
+      <c r="V13" s="10">
+        <v>75.3</v>
+      </c>
+      <c r="W13" s="5">
+        <v>75.3</v>
+      </c>
+      <c r="X13" s="5">
+        <v>75.2</v>
+      </c>
+      <c r="Y13" s="8"/>
       <c r="Z13" s="10"/>
-    </row>
-    <row r="14" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="AA13" s="10"/>
+      <c r="AB13" s="10"/>
+      <c r="AC13" s="10"/>
+      <c r="AD13" s="10"/>
+      <c r="AE13" s="10"/>
+      <c r="AF13" s="10"/>
+      <c r="AG13" s="10"/>
+      <c r="AH13" s="10"/>
+      <c r="AI13" s="10"/>
+      <c r="AJ13" s="10"/>
+      <c r="AK13" s="10"/>
+      <c r="AL13" s="10"/>
+      <c r="AM13" s="10"/>
+      <c r="AN13" s="10"/>
+      <c r="AO13" s="10"/>
+      <c r="AP13" s="10"/>
+    </row>
+    <row r="14" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>103</v>
       </c>
@@ -1326,59 +1604,105 @@
         <v>612.75422041204138</v>
       </c>
       <c r="I14" s="8"/>
-      <c r="J14" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>96</v>
+      <c r="J14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="10">
+        <v>76.099999999999994</v>
       </c>
       <c r="L14" s="10">
-        <v>385</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="M14" s="10">
-        <v>589.79999999999995</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="N14" s="10">
-        <v>74.7</v>
-      </c>
-      <c r="O14" s="10">
-        <v>75.599999999999994</v>
+        <v>76</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="P14" s="10">
         <v>75.5</v>
       </c>
       <c r="Q14" s="10">
+        <v>75.5</v>
+      </c>
+      <c r="R14" s="10">
+        <v>75.5</v>
+      </c>
+      <c r="S14" s="10">
+        <v>75.5</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="U14" s="10">
+        <v>75.2</v>
+      </c>
+      <c r="V14" s="10">
+        <v>75.2</v>
+      </c>
+      <c r="W14" s="5">
+        <v>75.2</v>
+      </c>
+      <c r="X14" s="5">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="Y14" s="8"/>
+      <c r="Z14" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA14" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB14" s="10">
+        <v>385</v>
+      </c>
+      <c r="AC14" s="10">
+        <v>589.79999999999995</v>
+      </c>
+      <c r="AD14" s="10">
+        <v>74.7</v>
+      </c>
+      <c r="AE14" s="10">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="AF14" s="10">
+        <v>75.5</v>
+      </c>
+      <c r="AG14" s="10">
         <v>75.400000000000006</v>
       </c>
-      <c r="R14" s="10">
+      <c r="AH14" s="10">
         <v>67.400000000000006</v>
       </c>
-      <c r="S14" s="10">
+      <c r="AI14" s="10">
         <v>435</v>
       </c>
-      <c r="T14" s="10">
+      <c r="AJ14" s="10">
         <v>44</v>
       </c>
-      <c r="U14" s="10">
+      <c r="AK14" s="10">
         <v>1135</v>
       </c>
-      <c r="V14" s="10">
+      <c r="AL14" s="10">
         <v>66</v>
       </c>
-      <c r="W14" s="10">
+      <c r="AM14" s="10">
         <v>100</v>
       </c>
-      <c r="X14" s="10">
+      <c r="AN14" s="10">
         <v>613</v>
       </c>
-      <c r="Y14" s="10">
+      <c r="AO14" s="10">
         <v>429</v>
       </c>
-      <c r="Z14" s="10">
+      <c r="AP14" s="10">
         <v>499</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>104</v>
       </c>
@@ -1406,59 +1730,105 @@
         <v>613.90492684228116</v>
       </c>
       <c r="I15" s="8"/>
-      <c r="J15" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>96</v>
+      <c r="J15" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="10">
+        <v>76</v>
       </c>
       <c r="L15" s="10">
-        <v>425</v>
+        <v>76</v>
       </c>
       <c r="M15" s="10">
-        <v>614.70000000000005</v>
+        <v>76</v>
       </c>
       <c r="N15" s="10">
-        <v>74.7</v>
-      </c>
-      <c r="O15" s="10">
-        <v>75.599999999999994</v>
+        <v>75.900000000000006</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="P15" s="10">
-        <v>75.5</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="Q15" s="10">
         <v>75.400000000000006</v>
       </c>
       <c r="R15" s="10">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="S15" s="10">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="U15" s="10">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="V15" s="10">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="W15" s="5">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="X15" s="5">
+        <v>75</v>
+      </c>
+      <c r="Y15" s="8"/>
+      <c r="Z15" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA15" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB15" s="10">
+        <v>425</v>
+      </c>
+      <c r="AC15" s="10">
+        <v>614.70000000000005</v>
+      </c>
+      <c r="AD15" s="10">
+        <v>74.7</v>
+      </c>
+      <c r="AE15" s="10">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="AF15" s="10">
+        <v>75.5</v>
+      </c>
+      <c r="AG15" s="10">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="AH15" s="10">
         <v>67.400000000000006</v>
       </c>
-      <c r="S15" s="10">
+      <c r="AI15" s="10">
         <v>435</v>
       </c>
-      <c r="T15" s="10">
+      <c r="AJ15" s="10">
         <v>44</v>
       </c>
-      <c r="U15" s="10">
+      <c r="AK15" s="10">
         <v>1160</v>
       </c>
-      <c r="V15" s="10">
+      <c r="AL15" s="10">
         <v>66</v>
       </c>
-      <c r="W15" s="10">
+      <c r="AM15" s="10">
         <v>100</v>
       </c>
-      <c r="X15" s="10">
+      <c r="AN15" s="10">
         <v>613</v>
       </c>
-      <c r="Y15" s="10">
+      <c r="AO15" s="10">
         <v>454</v>
       </c>
-      <c r="Z15" s="10">
+      <c r="AP15" s="10">
         <v>499</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -1480,59 +1850,105 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
       <c r="I16" s="8"/>
-      <c r="J16" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>96</v>
+      <c r="J16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="10">
+        <v>68</v>
       </c>
       <c r="L16" s="10">
-        <v>465</v>
+        <v>68</v>
       </c>
       <c r="M16" s="10">
-        <v>637.29999999999995</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="N16" s="10">
-        <v>74.7</v>
-      </c>
-      <c r="O16" s="10">
-        <v>75.599999999999994</v>
+        <v>67.900000000000006</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="P16" s="10">
-        <v>75.5</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="Q16" s="10">
-        <v>75.400000000000006</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="R16" s="10">
         <v>67.400000000000006</v>
       </c>
       <c r="S16" s="10">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="U16" s="10">
+        <v>67</v>
+      </c>
+      <c r="V16" s="10">
+        <v>67</v>
+      </c>
+      <c r="W16" s="5">
+        <v>67</v>
+      </c>
+      <c r="X16" s="5">
+        <v>67</v>
+      </c>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA16" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB16" s="10">
+        <v>465</v>
+      </c>
+      <c r="AC16" s="10">
+        <v>637.29999999999995</v>
+      </c>
+      <c r="AD16" s="10">
+        <v>74.7</v>
+      </c>
+      <c r="AE16" s="10">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="AF16" s="10">
+        <v>75.5</v>
+      </c>
+      <c r="AG16" s="10">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="AH16" s="10">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="AI16" s="10">
         <v>435</v>
       </c>
-      <c r="T16" s="10">
+      <c r="AJ16" s="10">
         <v>44</v>
       </c>
-      <c r="U16" s="10">
+      <c r="AK16" s="10">
         <v>1184</v>
       </c>
-      <c r="V16" s="10">
+      <c r="AL16" s="10">
         <v>66</v>
       </c>
-      <c r="W16" s="10">
+      <c r="AM16" s="10">
         <v>110</v>
       </c>
-      <c r="X16" s="10">
+      <c r="AN16" s="10">
         <v>622</v>
       </c>
-      <c r="Y16" s="10">
+      <c r="AO16" s="10">
         <v>474</v>
       </c>
-      <c r="Z16" s="10">
+      <c r="AP16" s="10">
         <v>499</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -1554,59 +1970,105 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
-      <c r="J17" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>96</v>
+      <c r="J17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="K17" s="10">
+        <v>435</v>
       </c>
       <c r="L17" s="10">
-        <v>510</v>
+        <v>435</v>
       </c>
       <c r="M17" s="10">
-        <v>667.5</v>
+        <v>435</v>
       </c>
       <c r="N17" s="10">
-        <v>74.7</v>
-      </c>
-      <c r="O17" s="10">
-        <v>75.599999999999994</v>
+        <v>435</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="P17" s="10">
-        <v>75.5</v>
+        <v>435</v>
       </c>
       <c r="Q17" s="10">
-        <v>75.400000000000006</v>
+        <v>435</v>
       </c>
       <c r="R17" s="10">
-        <v>67.400000000000006</v>
+        <v>435</v>
       </c>
       <c r="S17" s="10">
         <v>435</v>
       </c>
-      <c r="T17" s="10">
+      <c r="T17" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="U17" s="10">
+        <v>435</v>
+      </c>
+      <c r="V17" s="10">
+        <v>435</v>
+      </c>
+      <c r="W17" s="5">
+        <v>435</v>
+      </c>
+      <c r="X17" s="5">
+        <v>435</v>
+      </c>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA17" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB17" s="10">
+        <v>510</v>
+      </c>
+      <c r="AC17" s="10">
+        <v>667.5</v>
+      </c>
+      <c r="AD17" s="10">
+        <v>74.7</v>
+      </c>
+      <c r="AE17" s="10">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="AF17" s="10">
+        <v>75.5</v>
+      </c>
+      <c r="AG17" s="10">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="AH17" s="10">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="AI17" s="10">
+        <v>435</v>
+      </c>
+      <c r="AJ17" s="10">
         <v>44</v>
       </c>
-      <c r="U17" s="10">
+      <c r="AK17" s="10">
         <v>1216</v>
       </c>
-      <c r="V17" s="10">
+      <c r="AL17" s="10">
         <v>66</v>
       </c>
-      <c r="W17" s="10">
+      <c r="AM17" s="10">
         <v>130</v>
       </c>
-      <c r="X17" s="10">
+      <c r="AN17" s="10">
         <v>640</v>
       </c>
-      <c r="Y17" s="10">
+      <c r="AO17" s="10">
         <v>499</v>
       </c>
-      <c r="Z17" s="10">
+      <c r="AP17" s="10">
         <v>499</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
@@ -1628,25 +2090,71 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
       <c r="I18" s="8"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
+      <c r="J18" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K18" s="10">
+        <v>44</v>
+      </c>
+      <c r="L18" s="10">
+        <v>44</v>
+      </c>
+      <c r="M18" s="10">
+        <v>44</v>
+      </c>
+      <c r="N18" s="10">
+        <v>44</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="P18" s="10">
+        <v>44</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>44</v>
+      </c>
+      <c r="R18" s="10">
+        <v>44</v>
+      </c>
+      <c r="S18" s="10">
+        <v>44</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="U18" s="10">
+        <v>44</v>
+      </c>
+      <c r="V18" s="10">
+        <v>44</v>
+      </c>
+      <c r="W18" s="5">
+        <v>44</v>
+      </c>
+      <c r="X18" s="5">
+        <v>44</v>
+      </c>
+      <c r="Y18" s="8"/>
       <c r="Z18" s="10"/>
-    </row>
-    <row r="19" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="AA18" s="10"/>
+      <c r="AB18" s="10"/>
+      <c r="AC18" s="10"/>
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="10"/>
+      <c r="AF18" s="10"/>
+      <c r="AG18" s="10"/>
+      <c r="AH18" s="10"/>
+      <c r="AI18" s="10"/>
+      <c r="AJ18" s="10"/>
+      <c r="AK18" s="10"/>
+      <c r="AL18" s="10"/>
+      <c r="AM18" s="10"/>
+      <c r="AN18" s="10"/>
+      <c r="AO18" s="10"/>
+      <c r="AP18" s="10"/>
+    </row>
+    <row r="19" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
@@ -1668,59 +2176,105 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
-      <c r="J19" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>97</v>
+      <c r="J19" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K19" s="10">
+        <v>1130</v>
       </c>
       <c r="L19" s="10">
-        <v>385</v>
+        <v>1155</v>
       </c>
       <c r="M19" s="10">
-        <v>590.9</v>
+        <v>1179</v>
       </c>
       <c r="N19" s="10">
-        <v>74.3</v>
-      </c>
-      <c r="O19" s="10">
-        <v>75.3</v>
+        <v>1212</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="P19" s="10">
-        <v>75.2</v>
+        <v>1135</v>
       </c>
       <c r="Q19" s="10">
-        <v>75.099999999999994</v>
+        <v>1160</v>
       </c>
       <c r="R19" s="10">
-        <v>67</v>
+        <v>1184</v>
       </c>
       <c r="S19" s="10">
-        <v>435</v>
-      </c>
-      <c r="T19" s="10">
-        <v>44</v>
+        <v>1216</v>
+      </c>
+      <c r="T19" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="U19" s="10">
         <v>1138</v>
       </c>
       <c r="V19" s="10">
+        <v>1163</v>
+      </c>
+      <c r="W19" s="2">
+        <v>1187</v>
+      </c>
+      <c r="X19" s="2">
+        <v>1220</v>
+      </c>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB19" s="10">
+        <v>385</v>
+      </c>
+      <c r="AC19" s="10">
+        <v>590.9</v>
+      </c>
+      <c r="AD19" s="10">
+        <v>74.3</v>
+      </c>
+      <c r="AE19" s="10">
+        <v>75.3</v>
+      </c>
+      <c r="AF19" s="10">
+        <v>75.2</v>
+      </c>
+      <c r="AG19" s="10">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="AH19" s="10">
+        <v>67</v>
+      </c>
+      <c r="AI19" s="10">
+        <v>435</v>
+      </c>
+      <c r="AJ19" s="10">
+        <v>44</v>
+      </c>
+      <c r="AK19" s="10">
+        <v>1138</v>
+      </c>
+      <c r="AL19" s="10">
         <v>63</v>
       </c>
-      <c r="W19" s="10">
+      <c r="AM19" s="10">
         <v>100</v>
       </c>
-      <c r="X19" s="10">
+      <c r="AN19" s="10">
         <v>616</v>
       </c>
-      <c r="Y19" s="10">
+      <c r="AO19" s="10">
         <v>425</v>
       </c>
-      <c r="Z19" s="10">
+      <c r="AP19" s="10">
         <v>507</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
@@ -1742,59 +2296,105 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
       <c r="I20" s="8"/>
-      <c r="J20" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>97</v>
+      <c r="J20" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="K20" s="10">
+        <v>70</v>
       </c>
       <c r="L20" s="10">
-        <v>425</v>
+        <v>70</v>
       </c>
       <c r="M20" s="10">
-        <v>615.79999999999995</v>
+        <v>70</v>
       </c>
       <c r="N20" s="10">
-        <v>74.3</v>
-      </c>
-      <c r="O20" s="10">
-        <v>75.3</v>
+        <v>70</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="P20" s="10">
-        <v>75.2</v>
+        <v>66</v>
       </c>
       <c r="Q20" s="10">
-        <v>75.099999999999994</v>
+        <v>66</v>
       </c>
       <c r="R20" s="10">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S20" s="10">
-        <v>435</v>
-      </c>
-      <c r="T20" s="10">
-        <v>44</v>
+        <v>66</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="U20" s="10">
-        <v>1163</v>
+        <v>63</v>
       </c>
       <c r="V20" s="10">
         <v>63</v>
       </c>
-      <c r="W20" s="10">
+      <c r="W20" s="2">
+        <v>63</v>
+      </c>
+      <c r="X20" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y20" s="8"/>
+      <c r="Z20" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA20" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB20" s="10">
+        <v>425</v>
+      </c>
+      <c r="AC20" s="10">
+        <v>615.79999999999995</v>
+      </c>
+      <c r="AD20" s="10">
+        <v>74.3</v>
+      </c>
+      <c r="AE20" s="10">
+        <v>75.3</v>
+      </c>
+      <c r="AF20" s="10">
+        <v>75.2</v>
+      </c>
+      <c r="AG20" s="10">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="AH20" s="10">
+        <v>67</v>
+      </c>
+      <c r="AI20" s="10">
+        <v>435</v>
+      </c>
+      <c r="AJ20" s="10">
+        <v>44</v>
+      </c>
+      <c r="AK20" s="10">
+        <v>1163</v>
+      </c>
+      <c r="AL20" s="10">
+        <v>63</v>
+      </c>
+      <c r="AM20" s="10">
         <v>100</v>
       </c>
-      <c r="X20" s="10">
+      <c r="AN20" s="10">
         <v>616</v>
       </c>
-      <c r="Y20" s="10">
+      <c r="AO20" s="10">
         <v>450</v>
       </c>
-      <c r="Z20" s="10">
+      <c r="AP20" s="10">
         <v>507</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
@@ -1816,59 +2416,105 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
       <c r="I21" s="8"/>
-      <c r="J21" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="L21" s="8">
-        <v>465</v>
-      </c>
-      <c r="M21" s="8">
-        <v>638.4</v>
-      </c>
-      <c r="N21" s="5">
-        <v>74.3</v>
-      </c>
-      <c r="O21" s="5">
-        <v>75.3</v>
-      </c>
-      <c r="P21" s="5">
-        <v>75.2</v>
-      </c>
-      <c r="Q21" s="5">
-        <v>75.099999999999994</v>
-      </c>
-      <c r="R21" s="5">
-        <v>67</v>
-      </c>
-      <c r="S21" s="5">
-        <v>435</v>
-      </c>
-      <c r="T21" s="5">
-        <v>44</v>
-      </c>
-      <c r="U21" s="2">
-        <v>1187</v>
-      </c>
-      <c r="V21" s="2">
-        <v>63</v>
+      <c r="J21" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="K21" s="10">
+        <v>100</v>
+      </c>
+      <c r="L21" s="10">
+        <v>100</v>
+      </c>
+      <c r="M21" s="10">
+        <v>110</v>
+      </c>
+      <c r="N21" s="10">
+        <v>130</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P21" s="10">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>100</v>
+      </c>
+      <c r="R21" s="10">
+        <v>110</v>
+      </c>
+      <c r="S21" s="10">
+        <v>130</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="U21" s="10">
+        <v>100</v>
+      </c>
+      <c r="V21" s="10">
+        <v>100</v>
       </c>
       <c r="W21" s="2">
         <v>110</v>
       </c>
       <c r="X21" s="2">
+        <v>130</v>
+      </c>
+      <c r="Y21" s="8"/>
+      <c r="Z21" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA21" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB21" s="8">
+        <v>465</v>
+      </c>
+      <c r="AC21" s="8">
+        <v>638.4</v>
+      </c>
+      <c r="AD21" s="5">
+        <v>74.3</v>
+      </c>
+      <c r="AE21" s="5">
+        <v>75.3</v>
+      </c>
+      <c r="AF21" s="5">
+        <v>75.2</v>
+      </c>
+      <c r="AG21" s="5">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="AH21" s="5">
+        <v>67</v>
+      </c>
+      <c r="AI21" s="5">
+        <v>435</v>
+      </c>
+      <c r="AJ21" s="5">
+        <v>44</v>
+      </c>
+      <c r="AK21" s="2">
+        <v>1187</v>
+      </c>
+      <c r="AL21" s="2">
+        <v>63</v>
+      </c>
+      <c r="AM21" s="2">
+        <v>110</v>
+      </c>
+      <c r="AN21" s="2">
         <v>625</v>
       </c>
-      <c r="Y21" s="2">
+      <c r="AO21" s="2">
         <v>470</v>
       </c>
-      <c r="Z21" s="2">
+      <c r="AP21" s="2">
         <v>507</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
@@ -1890,59 +2536,105 @@
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
-      <c r="J22" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="L22" s="8">
-        <v>510</v>
-      </c>
-      <c r="M22" s="8">
-        <v>668.6</v>
-      </c>
-      <c r="N22" s="5">
-        <v>74.3</v>
-      </c>
-      <c r="O22" s="5">
-        <v>75.2</v>
-      </c>
-      <c r="P22" s="5">
-        <v>75.099999999999994</v>
-      </c>
-      <c r="Q22" s="5">
-        <v>75</v>
-      </c>
-      <c r="R22" s="5">
-        <v>67</v>
-      </c>
-      <c r="S22" s="5">
-        <v>435</v>
-      </c>
-      <c r="T22" s="5">
-        <v>44</v>
-      </c>
-      <c r="U22" s="2">
-        <v>1220</v>
-      </c>
-      <c r="V22" s="2">
-        <v>63</v>
+      <c r="J22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K22" s="10">
+        <v>608</v>
+      </c>
+      <c r="L22" s="10">
+        <v>608</v>
+      </c>
+      <c r="M22" s="10">
+        <v>617</v>
+      </c>
+      <c r="N22" s="10">
+        <v>635</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="P22" s="10">
+        <v>613</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>613</v>
+      </c>
+      <c r="R22" s="10">
+        <v>622</v>
+      </c>
+      <c r="S22" s="10">
+        <v>640</v>
+      </c>
+      <c r="T22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="U22" s="10">
+        <v>616</v>
+      </c>
+      <c r="V22" s="10">
+        <v>616</v>
       </c>
       <c r="W22" s="2">
-        <v>130</v>
+        <v>625</v>
       </c>
       <c r="X22" s="2">
         <v>643</v>
       </c>
-      <c r="Y22" s="2">
+      <c r="Y22" s="8"/>
+      <c r="Z22" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA22" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB22" s="8">
+        <v>510</v>
+      </c>
+      <c r="AC22" s="8">
+        <v>668.6</v>
+      </c>
+      <c r="AD22" s="5">
+        <v>74.3</v>
+      </c>
+      <c r="AE22" s="5">
+        <v>75.2</v>
+      </c>
+      <c r="AF22" s="5">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="AG22" s="5">
+        <v>75</v>
+      </c>
+      <c r="AH22" s="5">
+        <v>67</v>
+      </c>
+      <c r="AI22" s="5">
+        <v>435</v>
+      </c>
+      <c r="AJ22" s="5">
+        <v>44</v>
+      </c>
+      <c r="AK22" s="2">
+        <v>1220</v>
+      </c>
+      <c r="AL22" s="2">
+        <v>63</v>
+      </c>
+      <c r="AM22" s="2">
+        <v>130</v>
+      </c>
+      <c r="AN22" s="2">
+        <v>643</v>
+      </c>
+      <c r="AO22" s="2">
         <v>495</v>
       </c>
-      <c r="Z22" s="2">
+      <c r="AP22" s="2">
         <v>507</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>17</v>
       </c>
@@ -1964,20 +2656,66 @@
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-    </row>
-    <row r="24" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="J23" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="K23" s="10">
+        <v>436</v>
+      </c>
+      <c r="L23" s="10">
+        <v>460</v>
+      </c>
+      <c r="M23" s="10">
+        <v>480</v>
+      </c>
+      <c r="N23" s="10">
+        <v>505</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="P23" s="10">
+        <v>429</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>454</v>
+      </c>
+      <c r="R23" s="10">
+        <v>474</v>
+      </c>
+      <c r="S23" s="10">
+        <v>499</v>
+      </c>
+      <c r="T23" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="U23" s="10">
+        <v>425</v>
+      </c>
+      <c r="V23" s="10">
+        <v>450</v>
+      </c>
+      <c r="W23" s="2">
+        <v>470</v>
+      </c>
+      <c r="X23" s="2">
+        <v>495</v>
+      </c>
+      <c r="Y23" s="8"/>
+      <c r="Z23" s="8"/>
+      <c r="AA23" s="8"/>
+      <c r="AB23" s="8"/>
+      <c r="AC23" s="8"/>
+      <c r="AD23" s="4"/>
+      <c r="AE23" s="5"/>
+      <c r="AF23" s="5"/>
+      <c r="AG23" s="5"/>
+      <c r="AH23" s="5"/>
+      <c r="AI23" s="5"/>
+      <c r="AJ23" s="5"/>
+      <c r="AK23" s="5"/>
+    </row>
+    <row r="24" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -1999,20 +2737,66 @@
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-    </row>
-    <row r="25" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="J24" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="K24" s="10">
+        <v>486</v>
+      </c>
+      <c r="L24" s="10">
+        <v>486</v>
+      </c>
+      <c r="M24" s="10">
+        <v>486</v>
+      </c>
+      <c r="N24" s="10">
+        <v>486</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="P24" s="10">
+        <v>499</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>499</v>
+      </c>
+      <c r="R24" s="10">
+        <v>499</v>
+      </c>
+      <c r="S24" s="10">
+        <v>499</v>
+      </c>
+      <c r="T24" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="U24" s="10">
+        <v>507</v>
+      </c>
+      <c r="V24" s="10">
+        <v>507</v>
+      </c>
+      <c r="W24" s="2">
+        <v>507</v>
+      </c>
+      <c r="X24" s="2">
+        <v>507</v>
+      </c>
+      <c r="Y24" s="8"/>
+      <c r="Z24" s="8"/>
+      <c r="AA24" s="8"/>
+      <c r="AB24" s="8"/>
+      <c r="AC24" s="8"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="5"/>
+      <c r="AF24" s="5"/>
+      <c r="AG24" s="5"/>
+      <c r="AH24" s="5"/>
+      <c r="AI24" s="5"/>
+      <c r="AJ24" s="5"/>
+      <c r="AK24" s="5"/>
+    </row>
+    <row r="25" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -2038,16 +2822,32 @@
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
-    </row>
-    <row r="26" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="8"/>
+      <c r="AA25" s="8"/>
+      <c r="AB25" s="8"/>
+      <c r="AC25" s="8"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="5"/>
+      <c r="AF25" s="5"/>
+      <c r="AG25" s="5"/>
+      <c r="AH25" s="5"/>
+      <c r="AI25" s="5"/>
+      <c r="AJ25" s="5"/>
+      <c r="AK25" s="5"/>
+    </row>
+    <row r="26" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>101</v>
       </c>
@@ -2071,16 +2871,32 @@
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-    </row>
-    <row r="27" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="8"/>
+      <c r="Z26" s="8"/>
+      <c r="AA26" s="8"/>
+      <c r="AB26" s="8"/>
+      <c r="AC26" s="8"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="5"/>
+      <c r="AF26" s="5"/>
+      <c r="AG26" s="5"/>
+      <c r="AH26" s="5"/>
+      <c r="AI26" s="5"/>
+      <c r="AJ26" s="5"/>
+      <c r="AK26" s="5"/>
+    </row>
+    <row r="27" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>126</v>
       </c>
@@ -2104,16 +2920,32 @@
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
-    </row>
-    <row r="28" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8"/>
+      <c r="X27" s="8"/>
+      <c r="Y27" s="8"/>
+      <c r="Z27" s="8"/>
+      <c r="AA27" s="8"/>
+      <c r="AB27" s="8"/>
+      <c r="AC27" s="8"/>
+      <c r="AD27" s="4"/>
+      <c r="AE27" s="5"/>
+      <c r="AF27" s="5"/>
+      <c r="AG27" s="5"/>
+      <c r="AH27" s="5"/>
+      <c r="AI27" s="5"/>
+      <c r="AJ27" s="5"/>
+      <c r="AK27" s="5"/>
+    </row>
+    <row r="28" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>74</v>
       </c>
@@ -2129,16 +2961,32 @@
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
-    </row>
-    <row r="29" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="8"/>
+      <c r="Z28" s="8"/>
+      <c r="AA28" s="8"/>
+      <c r="AB28" s="8"/>
+      <c r="AC28" s="8"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="5"/>
+      <c r="AF28" s="5"/>
+      <c r="AG28" s="5"/>
+      <c r="AH28" s="5"/>
+      <c r="AI28" s="5"/>
+      <c r="AJ28" s="5"/>
+      <c r="AK28" s="5"/>
+    </row>
+    <row r="29" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>18</v>
       </c>
@@ -2154,16 +3002,32 @@
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
-    </row>
-    <row r="30" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
+      <c r="W29" s="8"/>
+      <c r="X29" s="8"/>
+      <c r="Y29" s="8"/>
+      <c r="Z29" s="8"/>
+      <c r="AA29" s="8"/>
+      <c r="AB29" s="8"/>
+      <c r="AC29" s="8"/>
+      <c r="AD29" s="4"/>
+      <c r="AE29" s="5"/>
+      <c r="AF29" s="5"/>
+      <c r="AG29" s="5"/>
+      <c r="AH29" s="5"/>
+      <c r="AI29" s="5"/>
+      <c r="AJ29" s="5"/>
+      <c r="AK29" s="5"/>
+    </row>
+    <row r="30" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>20</v>
       </c>
@@ -2179,16 +3043,32 @@
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-      <c r="U30" s="5"/>
-    </row>
-    <row r="31" spans="1:26" ht="22" x14ac:dyDescent="0.3">
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8"/>
+      <c r="X30" s="8"/>
+      <c r="Y30" s="8"/>
+      <c r="Z30" s="8"/>
+      <c r="AA30" s="8"/>
+      <c r="AB30" s="8"/>
+      <c r="AC30" s="8"/>
+      <c r="AD30" s="4"/>
+      <c r="AE30" s="5"/>
+      <c r="AF30" s="5"/>
+      <c r="AG30" s="5"/>
+      <c r="AH30" s="5"/>
+      <c r="AI30" s="5"/>
+      <c r="AJ30" s="5"/>
+      <c r="AK30" s="5"/>
+    </row>
+    <row r="31" spans="1:42" ht="22" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>21</v>
       </c>
@@ -2204,22 +3084,38 @@
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
       <c r="M31" s="8"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="8"/>
+      <c r="V31" s="8"/>
+      <c r="W31" s="8"/>
+      <c r="X31" s="8"/>
+      <c r="Y31" s="8"/>
+      <c r="Z31" s="8"/>
+      <c r="AA31" s="8"/>
+      <c r="AB31" s="8"/>
+      <c r="AC31" s="8"/>
+      <c r="AD31" s="4"/>
+      <c r="AE31" s="5"/>
+      <c r="AF31" s="5"/>
+      <c r="AG31" s="5"/>
+      <c r="AH31" s="5"/>
+      <c r="AI31" s="5"/>
+      <c r="AJ31" s="5"/>
+      <c r="AK31" s="5"/>
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>23</v>
       </c>
@@ -2228,7 +3124,7 @@
       </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>24</v>
       </c>
@@ -2248,7 +3144,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>25</v>
       </c>
@@ -2272,7 +3168,7 @@
         <v>60.959999999999994</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>26</v>
       </c>
@@ -2296,7 +3192,7 @@
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>27</v>
       </c>
@@ -2316,7 +3212,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>29</v>
       </c>
@@ -2336,10 +3232,10 @@
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L39" s="1"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AB39" s="1"/>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>31</v>
       </c>
@@ -2347,7 +3243,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>68</v>
       </c>
@@ -2355,7 +3251,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>69</v>
       </c>
@@ -2363,7 +3259,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>70</v>
       </c>
@@ -2371,7 +3267,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>33</v>
       </c>
@@ -2379,7 +3275,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>34</v>
       </c>
@@ -2387,12 +3283,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>36</v>
       </c>
@@ -2400,7 +3296,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>37</v>
       </c>
